--- a/projet1_stats_descriptives_depenses_sante_ocde copie.xlsx.xlsx
+++ b/projet1_stats_descriptives_depenses_sante_ocde copie.xlsx.xlsx
@@ -2,17 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
-  <fileSharing userName="Ctv" algorithmName="SHA-512" hashValue="7dshr8vU7jVoXsB8nQwm0/4BIJ69dT9qRRg/7PoC4yiLK2P78luJ1XYdpLXjSGS8+K33zoauckhFwjJGdsETyQ==" saltValue="61bG3qx6rtbAPko3OF1xcQ==" spinCount="100000"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ctv/Documents/LeCoinStat/Mes projets /"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ctv/Documents/LeCoinStat/Travaux/Publié/Projet 3 - Stat Univariée/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E7DF2A-E364-7941-A839-63C867834988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3088DFD7-E360-3843-80F2-ED2E85C579FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="zjketHzTxFkp+PuiJ3HYWukOk261eLnB4V8pfxTk56k6PnPlzaVCl8zH9sFtDu/co0ypZkzNfDpgRhZ+dq7G5A==" workbookSaltValue="7fBgVMjonujH21k0ZdXFYg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="onnées" sheetId="1" r:id="rId1"/>
@@ -579,7 +578,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>Health expenditure and financing</t>
   </si>
@@ -710,9 +709,6 @@
     <t>United States</t>
   </si>
   <si>
-    <t xml:space="preserve">© Terms &amp; conditions </t>
-  </si>
-  <si>
     <t>&lt;a  target="_blank" href="https://www.oecd.org/content/dam/oecd/en/publications/reports/2017/03/a-system-of-health-accounts-2011_g1g75c9d/9789264270985-en.pdf"&gt;A System of Health Accounts&lt;/a&gt; provides an updated and systematic description of the financial flows related to the consumption of healthcare goods and services. As demands for information increase and more countries implement and institutionalise health accounts according to the system, the data produced are expected to be more comparable, more detailed and more policy relevant. It builds on the original OECD Manual, published in 2000 to create a single global framework for producing health expenditure accounts that can help track resource flows from sources to uses. It is the result of a collaborative effort between the OECD, WHO and the European Commission, and sets out in more detail the boundaries, the definitions and the concepts – responding to healthcare systems around the globe – from the simplest to the more complicated. The accounting framework is organised around a tri-axial system for the recording of healthcare expenditure, namely classifications of the functions of healthcare (ICHA-HC), healthcare provision (ICHA-HP), and financing schemes (ICHA-HF).</t>
   </si>
   <si>
@@ -794,9 +790,6 @@
     <t>IQR</t>
   </si>
   <si>
-    <t>Observations</t>
-  </si>
-  <si>
     <t>Moyenne &gt; Mediane = asymétrie à droite</t>
   </si>
   <si>
@@ -824,29 +817,10 @@
     <t>mode pas pertinent pour variable continue</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">La distribution des dépenses de santé par habitant dans les pays de l'OCDE est asymétrique à droite (skewness = 0,91). La moyenne (3 885 €) est supérieure à la médiane (3 567€), signe que quelques valeurs élevées tirent la moyenne vers le haut. L'histogramme confirme cette lecture : 36 des 38 pays se concentrent entre 1 000 et 6 400 </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t>€</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve"> , tandis que les États-Unis (9 776,5 €) se situe très au-ddessus, à plus de 3 000 € du deuxième pays le plus dépensier (Suisse, 6 562€). Le kurtosis élevé (2,18) témoigne d 'une distribution concentrée autour du centre, mais avec une queue lourde causée par cette valeur extreme. </t>
-    </r>
-  </si>
-  <si>
     <t>distribution pointue,Leptokurtique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La distribution des dépenses de santé par habitant dans les pays de l'OCDE est asymétrique à droite (skewness = 0,91). La moyenne (3 885 €) est supérieure à la médiane (3 567€), signe que quelques valeurs élevées tirent la moyenne vers le haut. L'histogramme confirme cette lecture : 36 des 38 pays se concentrent entre 1 000 et 6 400 € , tandis que les États-Unis (9 776,5 €) se situe très au-ddessus, à plus de 3 000 € du deuxième pays le plus dépensier (Suisse, 6 562€). Le kurtosis élevé (2,18) témoigne d 'une distribution concentrée autour du centre, mais avec une queue lourde causée par cette valeur extreme. </t>
   </si>
 </sst>
 </file>
@@ -856,7 +830,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0\ _€"/>
   </numFmts>
-  <fonts count="98" x14ac:knownFonts="1">
+  <fonts count="92" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1316,33 +1290,33 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0563C1"/>
+      <color rgb="FF4182D5"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF4182D5"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1359,35 +1333,6 @@
       <color rgb="FF4182D5"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF4182D5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF4182D5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1396,25 +1341,14 @@
       <name val="Calibri (Corps)"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri (Corps)"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri (Corps)"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="95">
+  <fills count="93">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1922,39 +1856,13 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor auto="1"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor auto="1"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2120,7 +2028,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
@@ -2138,9 +2046,11 @@
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="85" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="86" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="86" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="85" fillId="87" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2156,130 +2066,118 @@
     <xf numFmtId="0" fontId="89" fillId="91" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="92" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="93" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="37" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="39" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="41" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="43" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="43" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="47" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="49" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="49" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="51" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="51" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="53" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="55" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="55" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="57" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="57" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="59" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="59" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="61" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="61" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="63" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="63" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="67" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="67" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="71" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="71" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="73" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="73" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="75" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="75" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="77" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="77" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="79" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="79" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="81" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="81" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="83" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="83" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2291,138 +2189,182 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="58" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="58" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="22" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="78" fillId="80" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="78" fillId="80" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="38" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="50" fillId="52" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="28" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="68" fillId="70" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="68" fillId="70" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="42" fillId="44" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="54" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="54" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="66" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="64" fillId="66" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="48" fillId="50" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="46" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="44" fillId="46" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="72" fillId="74" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="72" fillId="74" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="24" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="68" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="66" fillId="68" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="70" fillId="72" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="70" fillId="72" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="48" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="60" fillId="62" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="60" fillId="62" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="80" fillId="82" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="80" fillId="82" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="32" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="74" fillId="76" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="74" fillId="76" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="40" fillId="42" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="54" fillId="56" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="54" fillId="56" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="60" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="58" fillId="60" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="62" fillId="64" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="62" fillId="64" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="76" fillId="78" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="76" fillId="78" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="82" fillId="84" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="82" fillId="84" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="92" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="94" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2532,29 +2474,6 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2613,6 +2532,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.21715773809523811"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2653,7 +2580,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
+            <a:gradFill flip="none" rotWithShape="1">
               <a:gsLst>
                 <a:gs pos="0">
                   <a:schemeClr val="accent5">
@@ -2676,6 +2603,7 @@
               <a:path path="circle">
                 <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
               </a:path>
+              <a:tileRect/>
             </a:gradFill>
             <a:ln>
               <a:noFill/>
@@ -2690,62 +2618,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="fr-FR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -3067,12 +2940,13 @@
         <c:axId val="438881343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="28575" cap="flat" cmpd="thinThick" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3232,7 +3106,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{527102B3-FFFE-8C48-85DB-B32E2651E008}">
+        <cx:series layoutId="boxWhisker" uniqueId="{527102B3-FFFE-8C48-85DB-B32E2651E008}" formatIdx="0">
           <cx:spPr>
             <a:noFill/>
             <a:ln>
@@ -3346,7 +3220,7 @@
             </a:solidFill>
           </cx:spPr>
         </cx:plotSurface>
-        <cx:series layoutId="clusteredColumn" uniqueId="{9FD36DE8-8B8E-A14D-B160-BF1548A2ADDB}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{9FD36DE8-8B8E-A14D-B160-BF1548A2ADDB}" formatIdx="0">
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.2</cx:f>
@@ -5063,15 +4937,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>720132</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>166217</xdr:rowOff>
+      <xdr:colOff>42799</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>166215</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>174032</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>110533</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>927100</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>61451</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5100,16 +4974,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>58569</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>149423</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>272375</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>128257</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>94391</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -5145,8 +5019,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9964569" y="5864423"/>
-              <a:ext cx="5992306" cy="3979334"/>
+              <a:off x="8331200" y="4330700"/>
+              <a:ext cx="4572000" cy="4145691"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5178,16 +5052,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>600204</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>116021</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>671938</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>16933</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -5223,8 +5097,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9680704" y="1449521"/>
-              <a:ext cx="7501234" cy="3901412"/>
+              <a:off x="7150100" y="304801"/>
+              <a:ext cx="6286500" cy="3581400"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5258,24 +5132,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{74AC4960-4BB3-7141-A7CF-B6D97023225A}" name="Tableau3" displayName="Tableau3" ref="B7:C45" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{74AC4960-4BB3-7141-A7CF-B6D97023225A}" name="Tableau3" displayName="Tableau3" ref="B7:C45" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <autoFilter ref="B7:C45" xr:uid="{74AC4960-4BB3-7141-A7CF-B6D97023225A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:C45">
     <sortCondition ref="B7:B45"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61597AEC-793B-9F4B-9E3A-935E069D99E6}" name="Pays" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{8AFB5C3C-8C8F-6D40-B306-320EF120D5D5}" name="Dépenses de santé par habitants" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{61597AEC-793B-9F4B-9E3A-935E069D99E6}" name="Pays" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{8AFB5C3C-8C8F-6D40-B306-320EF120D5D5}" name="Dépenses de santé par habitants" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52F64984-3C32-F84A-A9BF-2BCBA46BCBEF}" name="Tableau1" displayName="Tableau1" ref="C4:D21" headerRowCount="0" headerRowDxfId="11">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E446466C-6CA2-CC44-A7BB-F683B450A5D8}" name="Colonne1" totalsRowLabel="Total" headerRowDxfId="10" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{CDE5BAB6-AC6D-744C-ABF0-91C09F0DAD7D}" name="Colonne2" totalsRowFunction="sum" headerRowDxfId="7" dataDxfId="6" totalsRowDxfId="5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52F64984-3C32-F84A-A9BF-2BCBA46BCBEF}" name="Tableau1" displayName="Tableau1" ref="B4:E21" headerRowCount="0" headerRowDxfId="8">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{E446466C-6CA2-CC44-A7BB-F683B450A5D8}" name="Colonne1" totalsRowLabel="Total" headerRowDxfId="7" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{CDE5BAB6-AC6D-744C-ABF0-91C09F0DAD7D}" name="Colonne2" totalsRowFunction="sum" headerRowDxfId="4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{573ABD89-8520-A147-8B5B-6CC14787AAD4}" name="Colonne5" headerRowDxfId="2" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{33392B81-F645-824D-B14C-C99F275FC9AF}" name="Colonne4" headerRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5544,11 +5420,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:D47"/>
+  <dimension ref="B1:C45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="63.33203125" customWidth="1"/>
-    <col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.2">
@@ -5577,592 +5455,676 @@
       </c>
     </row>
     <row r="7" spans="2:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
+    </row>
+    <row r="8" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="82">
         <v>5041.8289999999997</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="16" t="s">
+    <row r="9" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="91">
+      <c r="C9" s="87">
         <v>5604.3559999999998</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="88">
+      <c r="C10" s="84">
         <v>5120.12</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="82">
+      <c r="C11" s="78">
         <v>4631.6869999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="63">
         <v>2526.94</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="20" t="s">
+    <row r="13" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="55">
         <v>1288.529</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="21" t="s">
+    <row r="14" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="56">
         <v>1362.3879999999999</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="22" t="s">
+    <row r="15" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="70">
         <v>3462.96</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="23" t="s">
+    <row r="16" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="84">
+      <c r="C16" s="80">
         <v>4677.1540000000005</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="61">
         <v>2503.8780000000002</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="25" t="s">
+    <row r="18" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="75">
         <v>4180.799</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="26" t="s">
+    <row r="19" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="83">
+      <c r="C19" s="79">
         <v>4641.5720000000001</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="27" t="s">
+    <row r="20" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="93">
+      <c r="C20" s="89">
         <v>6242.1409999999996</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="28" t="s">
+    <row r="21" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="63">
+      <c r="C21" s="59">
         <v>2346.3490000000002</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="29" t="s">
+    <row r="22" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="62">
+      <c r="C22" s="58">
         <v>2090.75</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="30" t="s">
+    <row r="23" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="80">
+      <c r="C23" s="76">
         <v>4402.8969999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="31" t="s">
+    <row r="24" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="87">
+      <c r="C24" s="83">
         <v>5112.0029999999997</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="32" t="s">
+    <row r="25" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="68">
+      <c r="C25" s="64">
         <v>2656.0230000000001</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="33" t="s">
+    <row r="26" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="72">
+      <c r="C26" s="68">
         <v>3292.7280000000001</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="34" t="s">
+    <row r="27" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="77">
+      <c r="C27" s="73">
         <v>3623.828</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="35" t="s">
+    <row r="28" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="71">
+      <c r="C28" s="67">
         <v>3259.1790000000001</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="36" t="s">
+    <row r="29" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="64">
+      <c r="C29" s="60">
         <v>2446.442</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="37" t="s">
+    <row r="30" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="69">
+      <c r="C30" s="65">
         <v>2734.5770000000002</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="38" t="s">
+    <row r="31" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="89">
+      <c r="C31" s="85">
         <v>5237.2830000000004</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="39" t="s">
+    <row r="32" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="58">
+      <c r="C32" s="54">
         <v>1036.546</v>
       </c>
     </row>
-    <row r="33" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="40" t="s">
+    <row r="33" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="90">
+      <c r="C33" s="86">
         <v>5532.3429999999998</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="41" t="s">
+    <row r="34" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="78">
+      <c r="C34" s="74">
         <v>3737.8159999999998</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="42" t="s">
+    <row r="35" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="92">
+      <c r="C35" s="88">
         <v>5679.5789999999997</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="43" t="s">
+    <row r="36" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="70">
+      <c r="C36" s="66">
         <v>3163.6909999999998</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="44" t="s">
+    <row r="37" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="75">
+      <c r="C37" s="71">
         <v>3476.355</v>
       </c>
     </row>
-    <row r="38" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="45" t="s">
+    <row r="38" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="66">
+      <c r="C38" s="62">
         <v>2506.1709999999998</v>
       </c>
     </row>
-    <row r="39" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="46" t="s">
+    <row r="39" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="76">
+      <c r="C39" s="72">
         <v>3510.9009999999998</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="47" t="s">
+    <row r="40" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="73">
+      <c r="C40" s="69">
         <v>3338.8980000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="48" t="s">
+    <row r="41" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="85">
+      <c r="C41" s="81">
         <v>4824.9629999999997</v>
       </c>
     </row>
-    <row r="42" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="49" t="s">
+    <row r="42" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B42" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="94">
+      <c r="C42" s="90">
         <v>6562.1170000000002</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="50" t="s">
+    <row r="43" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B43" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="61">
+      <c r="C43" s="57">
         <v>1477.8920000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="51" t="s">
+    <row r="44" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B44" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="81">
+      <c r="C44" s="77">
         <v>4521.6909999999998</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="54" t="s">
+    <row r="45" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B45" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="91">
         <v>9776.4570000000003</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B47" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D47" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.27777777777777779" right="0.27777777777777779" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri (Corps),Gras"&amp;22&amp;UDonnées</oddHeader>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="664" max="16383" man="1"/>
+  </rowBreaks>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6441C4-8F69-E94B-98B9-A0BDDC31C5EB}">
-  <dimension ref="B2:K27"/>
+  <dimension ref="B1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="3.1640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="F2" s="96" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C4" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="55">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E1" s="92"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E2" s="92"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="51">
         <f>COUNTA(Tableau3[Dépenses de santé par habitants])</f>
         <v>38</v>
       </c>
-      <c r="F4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C5" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="56">
+      <c r="D4" s="93"/>
+      <c r="E4" s="92" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="52">
         <f>AVERAGE(Tableau3[Dépenses de santé par habitants])</f>
         <v>3885.048210526315</v>
       </c>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C6" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="56">
+      <c r="D5" s="94"/>
+      <c r="E5" s="92"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="52">
         <f>MEDIAN((Tableau3[]))</f>
         <v>3567.3644999999997</v>
       </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C7" s="55" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="56">
+      <c r="D6" s="94"/>
+      <c r="E6" s="92"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="52">
         <v>0</v>
       </c>
-      <c r="F7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C8" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="56">
+      <c r="D7" s="94"/>
+      <c r="E7" s="92" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="52">
         <f>+_xlfn.STDEV.S(Tableau3[])</f>
         <v>1733.726507952696</v>
       </c>
-      <c r="F8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C9" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="56">
-        <f>+_xlfn.VAR.S(Tableau3[])</f>
+      <c r="D8" s="94"/>
+      <c r="E8" s="92" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="51">
+        <f>_xlfn.VAR.S(Tableau3[#All])</f>
         <v>3005807.6043778495</v>
       </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C10" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="56">
+      <c r="D9" s="94"/>
+      <c r="E9" s="92"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="52">
         <f>MIN(Tableau3[])</f>
         <v>1036.546</v>
       </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C11" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="56">
+      <c r="D10" s="94"/>
+      <c r="E10" s="92"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="52">
         <f>MAX(Tableau3[])</f>
         <v>9776.4570000000003</v>
       </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C12" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="56">
+      <c r="D11" s="94"/>
+      <c r="E11" s="92"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="52">
         <f>MAX(Tableau3[])-MIN(Tableau3[])</f>
         <v>8739.9110000000001</v>
       </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C13" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="56">
+      <c r="D12" s="94"/>
+      <c r="E12" s="92"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="52">
         <f>STDEV(Tableau3[])/AVERAGE(Tableau3[])</f>
         <v>0.44625611163724138</v>
       </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C14" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="56">
+      <c r="D13" s="94"/>
+      <c r="E13" s="92"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="52">
         <f>_xlfn.QUARTILE.INC(Tableau3[],1)</f>
         <v>2559.2107500000002</v>
       </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C15" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="56">
+      <c r="D14" s="94"/>
+      <c r="E14" s="92"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="52">
         <f>_xlfn.QUARTILE.INC(Tableau3[],2)</f>
         <v>3567.3644999999997</v>
       </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C16" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="56">
+      <c r="D15" s="94"/>
+      <c r="E15" s="92"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="52">
         <f>_xlfn.QUARTILE.INC(Tableau3[],3)</f>
         <v>4987.6124999999993</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="C17" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="56">
+      <c r="D16" s="94"/>
+      <c r="E16" s="92"/>
+    </row>
+    <row r="17" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="52">
         <f>SKEW(Tableau3[])</f>
         <v>0.91467176100323688</v>
       </c>
-      <c r="F17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="C18" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="56">
+      <c r="D17" s="94"/>
+      <c r="E17" s="96" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="52">
         <f>KURT(Tableau3[])</f>
         <v>2.1807521505825154</v>
       </c>
-      <c r="F18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="C19" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="56">
-        <f>D16-D14</f>
+      <c r="D18" s="94"/>
+      <c r="E18" s="92" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="52">
+        <f>C16-C14</f>
         <v>2428.4017499999991</v>
       </c>
-      <c r="F19" s="57" t="s">
+      <c r="D19" s="94"/>
+      <c r="E19" s="95" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B20" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="52">
+        <f>C14-1.5*C19</f>
+        <v>-1083.3918749999984</v>
+      </c>
+      <c r="D20" s="94"/>
+      <c r="E20" s="93"/>
+    </row>
+    <row r="21" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B21" s="53" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="C20" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" s="56">
-        <f>D14-1.5*D19</f>
-        <v>-1083.3918749999984</v>
-      </c>
-      <c r="F20" s="55"/>
-    </row>
-    <row r="21" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="51">
+        <f>C16+1.5*C19</f>
+        <v>8630.2151249999988</v>
+      </c>
+      <c r="D21" s="93"/>
+      <c r="E21" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="55">
-        <f>D16+1.5*D19</f>
-        <v>8630.2151249999988</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="B24" s="97"/>
-      <c r="C24" s="100" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="101"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="100"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="100"/>
       <c r="C25" s="100"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="100"/>
       <c r="C26" s="100"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="C27" s="100"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="97"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="92"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="97"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="92"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E30" s="92"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E31" s="92"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E32" s="92"/>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E33" s="92"/>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="92"/>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="92"/>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E36" s="92"/>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E37" s="92"/>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E38" s="92"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E39" s="92"/>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E40" s="92"/>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E41" s="92"/>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E42" s="92"/>
+    </row>
+    <row r="43" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E43" s="92"/>
+    </row>
+    <row r="44" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E44" s="92"/>
+    </row>
+    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D24:K27"/>
-    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="B23:C26"/>
+    <mergeCell ref="D23:E27"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.27777777777777779" right="0.27777777777777779" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri Light (En-têtes),Gras"&amp;22&amp;UStatistiques descriptives</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -6171,71 +6133,1825 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3F4C52-C72D-A945-8696-6CF66ABEEFFF}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="0.1640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="1.83203125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0.1640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+  </cols>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.27777777777777779" right="0.19444444444444445" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri Light (En-têtes),Gras"&amp;22&amp;U&amp;K000000Graphiques</oddHeader>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="664" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:B15"/>
+  <dimension ref="B1:B624"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="115" style="8" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="83.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:2" ht="208" x14ac:dyDescent="0.2">
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="8" t="s">
+    <row r="7" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="8" t="s">
+    <row r="8" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="8" t="s">
+    <row r="11" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="10" t="s">
+    <row r="12" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="11" t="s">
+    <row r="13" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="12" t="s">
+    <row r="14" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="13" t="s">
+    <row r="15" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="14" t="s">
-        <v>52</v>
-      </c>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B46"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B47"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B48"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B58"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B59"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B60"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B61"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B62"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B63"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B64"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B68"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B69"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B70"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B71"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B72"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B73"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B74"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B75"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B76"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B77"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B78"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B79"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B80"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B81"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B82"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B84"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B85"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B86"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B87"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B88"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B94"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B95"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B96"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B104"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B105"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B106"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B107"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B109"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B110"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B111"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B112"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B187"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B188"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B192"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B193"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B194"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B195"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B196"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B197"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B198"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B199"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B200"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B201"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B202"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B203"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B204"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B205"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B206"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B207"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B208"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B209"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B210"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B211"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B212"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B213"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B214"/>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B215"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B216"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B217"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B218"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B219"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B220"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B222"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223"/>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224"/>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B225"/>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B226"/>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B227"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B228"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B229"/>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B230"/>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B231"/>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232"/>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B233"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B235"/>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B236"/>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B237"/>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B238"/>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B239"/>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B240"/>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B241"/>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B242"/>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B243"/>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B244"/>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B245"/>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B246"/>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B247"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B248"/>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B249"/>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B250"/>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B251"/>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B252"/>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B253"/>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B254"/>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B255"/>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B256"/>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B257"/>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B258"/>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B259"/>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B260"/>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B261"/>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B262"/>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B263"/>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B264"/>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B265"/>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B266"/>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B267"/>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B268"/>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B269"/>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B270"/>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B271"/>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B272"/>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B273"/>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B274"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B275"/>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B276"/>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B277"/>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B278"/>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B279"/>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B280"/>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B281"/>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B282"/>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B283"/>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B284"/>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B285"/>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B286"/>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B287"/>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B288"/>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B289"/>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B290"/>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B291"/>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B292"/>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B293"/>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B294"/>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B295"/>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B296"/>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B297"/>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B298"/>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B299"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B300"/>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B301"/>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B302"/>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B303"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B304"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B305"/>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B306"/>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B307"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B308"/>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B309"/>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B310"/>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B311"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B312"/>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B313"/>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B314"/>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B315"/>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B316"/>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B317"/>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B318"/>
+    </row>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B319"/>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B320"/>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B321"/>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B322"/>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B323"/>
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B324"/>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B325"/>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B326"/>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B327"/>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B328"/>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B329"/>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B330"/>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B331"/>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B332"/>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B333"/>
+    </row>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B334"/>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B335"/>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B336"/>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B337"/>
+    </row>
+    <row r="338" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B338"/>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B339"/>
+    </row>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B340"/>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B341"/>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B342"/>
+    </row>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B343"/>
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B344"/>
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B345"/>
+    </row>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B346"/>
+    </row>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B347"/>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B348"/>
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B349"/>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B350"/>
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B351"/>
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B352"/>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B353"/>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B354"/>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B355"/>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B356"/>
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B357"/>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B358"/>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B359"/>
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B360"/>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B361"/>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B362"/>
+    </row>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B363"/>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B364"/>
+    </row>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B365"/>
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B366"/>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B367"/>
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B368"/>
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B369"/>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B370"/>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B371"/>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B372"/>
+    </row>
+    <row r="373" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B373"/>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B374"/>
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B375"/>
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B376"/>
+    </row>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B377"/>
+    </row>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B378"/>
+    </row>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B379"/>
+    </row>
+    <row r="380" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B380"/>
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B381"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B382"/>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B383"/>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B384"/>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B385"/>
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B386"/>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B387"/>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B388"/>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B389"/>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B390"/>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B391"/>
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B392"/>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B393"/>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B394"/>
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B395"/>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B396"/>
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B397"/>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B398"/>
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B399"/>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B400"/>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B401"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B402"/>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B403"/>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B404"/>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B405"/>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B406"/>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B407"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B408"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B409"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B410"/>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B411"/>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B412"/>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B413"/>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B414"/>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B415"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B416"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B417"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B418"/>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B419"/>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B420"/>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B421"/>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B422"/>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B423"/>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B424"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B425"/>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B426"/>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B427"/>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B428"/>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B429"/>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B430"/>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B431"/>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B432"/>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B433"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B434"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B435"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B436"/>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B437"/>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B438"/>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B439"/>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B440"/>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B441"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B442"/>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B443"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B444"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B445"/>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B446"/>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B447"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B448"/>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B449"/>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B450"/>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B451"/>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B452"/>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B453"/>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B454"/>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B455"/>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B456"/>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B457"/>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B458"/>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B459"/>
+    </row>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B460"/>
+    </row>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B461"/>
+    </row>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B462"/>
+    </row>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B463"/>
+    </row>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B464"/>
+    </row>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B465"/>
+    </row>
+    <row r="466" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B466"/>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B467"/>
+    </row>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B468"/>
+    </row>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B469"/>
+    </row>
+    <row r="470" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B470"/>
+    </row>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B471"/>
+    </row>
+    <row r="472" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B472"/>
+    </row>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B473"/>
+    </row>
+    <row r="474" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B474"/>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B475"/>
+    </row>
+    <row r="476" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B476"/>
+    </row>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B477"/>
+    </row>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B478"/>
+    </row>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B479"/>
+    </row>
+    <row r="480" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B480"/>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B481"/>
+    </row>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B482"/>
+    </row>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B483"/>
+    </row>
+    <row r="484" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B484"/>
+    </row>
+    <row r="485" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B485"/>
+    </row>
+    <row r="486" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B486"/>
+    </row>
+    <row r="487" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B487"/>
+    </row>
+    <row r="488" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B488"/>
+    </row>
+    <row r="489" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B489"/>
+    </row>
+    <row r="490" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B490"/>
+    </row>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B491"/>
+    </row>
+    <row r="492" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B492"/>
+    </row>
+    <row r="493" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B493"/>
+    </row>
+    <row r="494" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B494"/>
+    </row>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B495"/>
+    </row>
+    <row r="496" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B496"/>
+    </row>
+    <row r="497" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B497"/>
+    </row>
+    <row r="498" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B498"/>
+    </row>
+    <row r="499" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B499"/>
+    </row>
+    <row r="500" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B500"/>
+    </row>
+    <row r="501" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B501"/>
+    </row>
+    <row r="502" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B502"/>
+    </row>
+    <row r="503" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B503"/>
+    </row>
+    <row r="504" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B504"/>
+    </row>
+    <row r="505" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B505"/>
+    </row>
+    <row r="506" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B506"/>
+    </row>
+    <row r="507" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B507"/>
+    </row>
+    <row r="508" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B508"/>
+    </row>
+    <row r="509" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B509"/>
+    </row>
+    <row r="510" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B510"/>
+    </row>
+    <row r="511" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B511"/>
+    </row>
+    <row r="512" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B512"/>
+    </row>
+    <row r="513" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B513"/>
+    </row>
+    <row r="514" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B514"/>
+    </row>
+    <row r="515" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B515"/>
+    </row>
+    <row r="516" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B516"/>
+    </row>
+    <row r="517" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B517"/>
+    </row>
+    <row r="518" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B518"/>
+    </row>
+    <row r="519" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B519"/>
+    </row>
+    <row r="520" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B520"/>
+    </row>
+    <row r="521" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B521"/>
+    </row>
+    <row r="522" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B522"/>
+    </row>
+    <row r="523" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B523"/>
+    </row>
+    <row r="524" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B524"/>
+    </row>
+    <row r="525" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B525"/>
+    </row>
+    <row r="526" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B526"/>
+    </row>
+    <row r="527" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B527"/>
+    </row>
+    <row r="528" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B528"/>
+    </row>
+    <row r="529" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B529"/>
+    </row>
+    <row r="530" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B530"/>
+    </row>
+    <row r="531" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B531"/>
+    </row>
+    <row r="532" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B532"/>
+    </row>
+    <row r="533" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B533"/>
+    </row>
+    <row r="534" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B534"/>
+    </row>
+    <row r="535" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B535"/>
+    </row>
+    <row r="536" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B536"/>
+    </row>
+    <row r="537" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B537"/>
+    </row>
+    <row r="538" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B538"/>
+    </row>
+    <row r="539" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B539"/>
+    </row>
+    <row r="540" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B540"/>
+    </row>
+    <row r="541" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B541"/>
+    </row>
+    <row r="542" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B542"/>
+    </row>
+    <row r="543" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B543"/>
+    </row>
+    <row r="544" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B544"/>
+    </row>
+    <row r="545" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B545"/>
+    </row>
+    <row r="546" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B546"/>
+    </row>
+    <row r="547" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B547"/>
+    </row>
+    <row r="548" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B548"/>
+    </row>
+    <row r="549" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B549"/>
+    </row>
+    <row r="550" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B550"/>
+    </row>
+    <row r="551" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B551"/>
+    </row>
+    <row r="552" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B552"/>
+    </row>
+    <row r="553" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B553"/>
+    </row>
+    <row r="554" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B554"/>
+    </row>
+    <row r="555" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B555"/>
+    </row>
+    <row r="556" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B556"/>
+    </row>
+    <row r="557" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B557"/>
+    </row>
+    <row r="558" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B558"/>
+    </row>
+    <row r="559" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B559"/>
+    </row>
+    <row r="560" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B560"/>
+    </row>
+    <row r="561" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B561"/>
+    </row>
+    <row r="562" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B562"/>
+    </row>
+    <row r="563" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B563"/>
+    </row>
+    <row r="564" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B564"/>
+    </row>
+    <row r="565" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B565"/>
+    </row>
+    <row r="566" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B566"/>
+    </row>
+    <row r="567" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B567"/>
+    </row>
+    <row r="568" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B568"/>
+    </row>
+    <row r="569" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B569"/>
+    </row>
+    <row r="570" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B570"/>
+    </row>
+    <row r="571" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B571"/>
+    </row>
+    <row r="572" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B572"/>
+    </row>
+    <row r="573" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B573"/>
+    </row>
+    <row r="574" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B574"/>
+    </row>
+    <row r="575" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B575"/>
+    </row>
+    <row r="576" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B576"/>
+    </row>
+    <row r="577" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B577"/>
+    </row>
+    <row r="578" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B578"/>
+    </row>
+    <row r="579" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B579"/>
+    </row>
+    <row r="580" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B580"/>
+    </row>
+    <row r="581" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B581"/>
+    </row>
+    <row r="582" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B582"/>
+    </row>
+    <row r="583" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B583"/>
+    </row>
+    <row r="584" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B584"/>
+    </row>
+    <row r="585" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B585"/>
+    </row>
+    <row r="586" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B586"/>
+    </row>
+    <row r="587" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B587"/>
+    </row>
+    <row r="588" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B588"/>
+    </row>
+    <row r="589" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B589"/>
+    </row>
+    <row r="590" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B590"/>
+    </row>
+    <row r="591" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B591"/>
+    </row>
+    <row r="592" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B592"/>
+    </row>
+    <row r="593" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B593"/>
+    </row>
+    <row r="594" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B594"/>
+    </row>
+    <row r="595" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B595"/>
+    </row>
+    <row r="596" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B596"/>
+    </row>
+    <row r="597" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B597"/>
+    </row>
+    <row r="598" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B598"/>
+    </row>
+    <row r="599" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B599"/>
+    </row>
+    <row r="600" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B600"/>
+    </row>
+    <row r="601" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B601"/>
+    </row>
+    <row r="602" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B602"/>
+    </row>
+    <row r="603" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B603"/>
+    </row>
+    <row r="604" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B604"/>
+    </row>
+    <row r="605" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B605"/>
+    </row>
+    <row r="606" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B606"/>
+    </row>
+    <row r="607" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B607"/>
+    </row>
+    <row r="608" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B608"/>
+    </row>
+    <row r="609" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B609"/>
+    </row>
+    <row r="610" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B610"/>
+    </row>
+    <row r="611" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B611"/>
+    </row>
+    <row r="612" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B612"/>
+    </row>
+    <row r="613" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B613"/>
+    </row>
+    <row r="614" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B614"/>
+    </row>
+    <row r="615" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B615"/>
+    </row>
+    <row r="616" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B616"/>
+    </row>
+    <row r="617" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B617"/>
+    </row>
+    <row r="618" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B618"/>
+    </row>
+    <row r="619" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B619"/>
+    </row>
+    <row r="620" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B620"/>
+    </row>
+    <row r="621" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B621"/>
+    </row>
+    <row r="622" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B622"/>
+    </row>
+    <row r="623" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B623"/>
+    </row>
+    <row r="624" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B624"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6244,6 +7960,10 @@
     <hyperlink ref="B14" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="B15" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.27777777777777779" right="0.27777777777777779" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="664" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>